--- a/Sample_3_International_Masters_College.xlsx
+++ b/Sample_3_International_Masters_College.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1989/Downloads/files (1)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC33BFD-26BA-7441-B945-9842328B611E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E1A54F-99A9-594A-8F95-CC4BF030BED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="151">
   <si>
     <t>INSTITUTION</t>
   </si>
@@ -30,9 +30,6 @@
     <t>Institution Name</t>
   </si>
   <si>
-    <t>Cambridge Global Institute of Management</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -48,9 +45,6 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>registrar@cgim.ac.uk</t>
-  </si>
-  <si>
     <t>CLASS / BATCH</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>Teacher Name</t>
   </si>
   <si>
-    <t>Prof. Dr. James Whitfield (Program Director)</t>
-  </si>
-  <si>
     <t>SUBJECTS</t>
   </si>
   <si>
@@ -463,13 +454,34 @@
   </si>
   <si>
     <t>To use: Open Student Insight App -&gt; Import Filled Excel -&gt; select this file.</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Usage Mode</t>
+  </si>
+  <si>
+    <t>institution</t>
+  </si>
+  <si>
+    <t>Hakki Global Institute of Management</t>
+  </si>
+  <si>
+    <t>registrar@hakki.ac.uk</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Sandeep Hakki (Program Director)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +508,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -540,10 +560,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -554,8 +575,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -856,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -865,191 +890,191 @@
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1"/>
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1"/>
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1"/>
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="2">
-        <v>100</v>
+        <v>27</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2">
-        <v>100</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2">
         <v>100</v>
       </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B23" s="2">
         <v>100</v>
       </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2">
         <v>100</v>
@@ -1057,53 +1082,53 @@
     </row>
     <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="B25" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B26" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="2">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="2">
-        <v>100</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2">
         <v>100</v>
@@ -1111,37 +1136,37 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="B32" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B33" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="2">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" s="2">
-        <v>100</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B36" s="2">
         <v>100</v>
@@ -1149,7 +1174,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B37" s="2">
         <v>100</v>
@@ -1157,7 +1182,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B38" s="2">
         <v>100</v>
@@ -1165,37 +1190,37 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B39" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="B40" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="2">
-        <v>100</v>
+        <v>51</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" s="2">
-        <v>100</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B43" s="2">
         <v>100</v>
@@ -1203,7 +1228,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B44" s="2">
         <v>100</v>
@@ -1211,75 +1236,94 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="1"/>
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" s="2">
-        <v>2</v>
-      </c>
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B49" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="B51" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="B55" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{A87624C8-CDA4-4F43-A76D-884EA6C550FF}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1297,108 +1341,108 @@
   <sheetData>
     <row r="1" spans="1:31" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2">
         <v>89</v>
@@ -1473,18 +1517,18 @@
         <v>0</v>
       </c>
       <c r="AE2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D3">
         <v>86</v>
@@ -1559,18 +1603,18 @@
         <v>0</v>
       </c>
       <c r="AE3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4">
         <v>83</v>
@@ -1645,18 +1689,18 @@
         <v>0</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D5">
         <v>76</v>
@@ -1731,18 +1775,18 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D6">
         <v>65</v>
@@ -1817,18 +1861,18 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>64</v>
@@ -1903,18 +1947,18 @@
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D8">
         <v>62</v>
@@ -1989,18 +2033,18 @@
         <v>0</v>
       </c>
       <c r="AE8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>61</v>
@@ -2075,18 +2119,18 @@
         <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D10">
         <v>53</v>
@@ -2161,18 +2205,18 @@
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -2247,18 +2291,18 @@
         <v>0</v>
       </c>
       <c r="AE11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12">
         <v>38</v>
@@ -2333,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="AE12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13">
         <v>29</v>
@@ -2419,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2437,37 +2481,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
